--- a/output/exim siva makadi.Invo_output.xlsx
+++ b/output/exim siva makadi.Invo_output.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -74,6 +74,10 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -83,19 +87,19 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P124"/>
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -478,10 +482,11 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="33" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,20 +552,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>earlyBooking2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>calculations</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Amount-hotel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Total price</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -605,7 +615,10 @@
       <c r="L2" s="3" t="n">
         <v>45550</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -613,13 +626,13 @@
 </t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>341</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -662,7 +675,10 @@
       <c r="L3" s="6" t="n">
         <v>45552</v>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -670,13 +686,13 @@
 </t>
         </is>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="Q3" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -719,7 +735,10 @@
       <c r="L4" s="3" t="n">
         <v>45553</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -727,13 +746,13 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -776,7 +795,10 @@
       <c r="L5" s="6" t="n">
         <v>45553</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -784,13 +806,13 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -833,7 +855,10 @@
       <c r="L6" s="3" t="n">
         <v>45570</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -841,13 +866,13 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>341</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -890,7 +915,10 @@
       <c r="L7" s="6" t="n">
         <v>45454</v>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -898,13 +926,13 @@
 </t>
         </is>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="O7" s="5" t="n">
         <v>741</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="P7" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -947,7 +975,10 @@
       <c r="L8" s="3" t="n">
         <v>45454</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -955,13 +986,13 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>1074</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>858</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>-216</v>
       </c>
     </row>
@@ -1004,7 +1035,10 @@
       <c r="L9" s="6" t="n">
         <v>45454</v>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -1012,13 +1046,13 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>741</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -1061,7 +1095,10 @@
       <c r="L10" s="3" t="n">
         <v>45481</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1069,13 +1106,13 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>517</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -1118,7 +1155,10 @@
       <c r="L11" s="6" t="n">
         <v>45481</v>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1126,13 +1166,13 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="O11" s="5" t="n">
         <v>517</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -1175,7 +1215,10 @@
       <c r="L12" s="3" t="n">
         <v>45429</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1183,13 +1226,13 @@
 </t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>517</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -1232,7 +1275,10 @@
       <c r="L13" s="6" t="n">
         <v>45614</v>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1240,13 +1286,13 @@
 </t>
         </is>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="O13" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="P13" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1289,7 +1335,10 @@
       <c r="L14" s="3" t="n">
         <v>45614</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1297,13 +1346,13 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1346,7 +1395,10 @@
       <c r="L15" s="6" t="n">
         <v>45532</v>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -1354,13 +1406,13 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>716</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1403,7 +1455,10 @@
       <c r="L16" s="3" t="n">
         <v>45532</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -1411,13 +1466,13 @@
 </t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>741</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -1460,7 +1515,10 @@
       <c r="L17" s="6" t="n">
         <v>45618</v>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1468,13 +1526,13 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>696</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="P17" s="5" t="n">
         <v>546</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="Q17" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -1517,7 +1575,10 @@
       <c r="L18" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -1525,13 +1586,13 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>828</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1574,7 +1635,10 @@
       <c r="L19" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1582,13 +1646,13 @@
 </t>
         </is>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="O19" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="P19" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1631,7 +1695,10 @@
       <c r="L20" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1639,13 +1706,13 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="O20" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1688,7 +1755,10 @@
       <c r="L21" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1696,13 +1766,13 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="O21" s="5" t="n">
         <v>436</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="P21" s="5" t="n">
         <v>336</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="Q21" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1745,7 +1815,10 @@
       <c r="L22" s="3" t="n">
         <v>45559</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1753,13 +1826,13 @@
 </t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1802,7 +1875,10 @@
       <c r="L23" s="6" t="n">
         <v>45562</v>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1810,13 +1886,13 @@
 </t>
         </is>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="P23" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="Q23" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1859,7 +1935,10 @@
       <c r="L24" s="3" t="n">
         <v>45576</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1867,13 +1946,13 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="O24" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1916,7 +1995,10 @@
       <c r="L25" s="6" t="n">
         <v>45590</v>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -1924,13 +2006,13 @@
 </t>
         </is>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="O25" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="P25" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="Q25" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1978,15 +2060,18 @@
         <v>45597</v>
       </c>
       <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
         <v/>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="O26" s="2" t="n">
         <v>665</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v/>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -2029,7 +2114,10 @@
       <c r="L27" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -2037,13 +2125,13 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="O27" s="5" t="n">
         <v>884</v>
       </c>
-      <c r="O27" s="5" t="n">
+      <c r="P27" s="5" t="n">
         <v>784</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="Q27" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2086,7 +2174,10 @@
       <c r="L28" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2094,13 +2185,13 @@
 </t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2143,7 +2234,10 @@
       <c r="L29" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2151,13 +2245,13 @@
 </t>
         </is>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>467</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="P29" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -2200,7 +2294,10 @@
       <c r="L30" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2208,13 +2305,13 @@
 </t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="O30" s="2" t="n">
         <v>316</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2257,7 +2354,10 @@
       <c r="L31" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2265,13 +2365,13 @@
 </t>
         </is>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="O31" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="P31" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2314,7 +2414,10 @@
       <c r="L32" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2322,13 +2425,13 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="O32" s="2" t="n">
         <v>696</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -2371,7 +2474,10 @@
       <c r="L33" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2379,13 +2485,13 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="O33" s="5" t="n">
         <v>517</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="P33" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -2428,7 +2534,10 @@
       <c r="L34" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2436,13 +2545,13 @@
 </t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O34" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2485,7 +2594,10 @@
       <c r="L35" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2493,13 +2605,13 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2542,7 +2654,10 @@
       <c r="L36" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2550,13 +2665,13 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2599,7 +2714,10 @@
       <c r="L37" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2607,13 +2725,13 @@
 </t>
         </is>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="P37" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2656,7 +2774,10 @@
       <c r="L38" s="3" t="n">
         <v>45525</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2664,13 +2785,13 @@
 </t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="O38" s="2" t="n">
         <v>517</v>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -2713,7 +2834,10 @@
       <c r="L39" s="6" t="n">
         <v>45526</v>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2721,13 +2845,13 @@
 </t>
         </is>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="O39" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2770,7 +2894,10 @@
       <c r="L40" s="3" t="n">
         <v>45526</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2778,13 +2905,13 @@
 </t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="O40" s="2" t="n">
         <v>517</v>
       </c>
-      <c r="O40" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -2827,7 +2954,10 @@
       <c r="L41" s="6" t="n">
         <v>45534</v>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2835,13 +2965,13 @@
 </t>
         </is>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="O41" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="P41" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="Q41" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2884,7 +3014,10 @@
       <c r="L42" s="3" t="n">
         <v>45561</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2892,13 +3025,13 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="O42" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O42" s="2" t="n">
+      <c r="P42" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2941,7 +3074,10 @@
       <c r="L43" s="6" t="n">
         <v>45575</v>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -2949,13 +3085,13 @@
 </t>
         </is>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="O43" s="5" t="n">
         <v>341</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="P43" s="5" t="n">
         <v>266</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -2998,7 +3134,10 @@
       <c r="L44" s="3" t="n">
         <v>45580</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3006,13 +3145,13 @@
 </t>
         </is>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="O44" s="2" t="n">
         <v>696</v>
       </c>
-      <c r="O44" s="2" t="n">
+      <c r="P44" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -3055,7 +3194,10 @@
       <c r="L45" s="6" t="n">
         <v>45591</v>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3063,13 +3205,13 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="O45" s="5" t="n">
         <v>548</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="P45" s="5" t="n">
         <v>448</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="Q45" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3112,7 +3254,10 @@
       <c r="L46" s="3" t="n">
         <v>45593</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3120,13 +3265,13 @@
 </t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="O46" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O46" s="2" t="n">
+      <c r="P46" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P46" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3169,7 +3314,10 @@
       <c r="L47" s="6" t="n">
         <v>45595</v>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3177,13 +3325,13 @@
 </t>
         </is>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="O47" s="5" t="n">
         <v>721</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="P47" s="5" t="n">
         <v>546</v>
       </c>
-      <c r="P47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>-175</v>
       </c>
     </row>
@@ -3226,7 +3374,10 @@
       <c r="L48" s="3" t="n">
         <v>45596</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3234,13 +3385,13 @@
 </t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="O48" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O48" s="2" t="n">
+      <c r="P48" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P48" s="4" t="n">
+      <c r="Q48" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3283,7 +3434,10 @@
       <c r="L49" s="6" t="n">
         <v>45596</v>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3291,13 +3445,13 @@
 </t>
         </is>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="O49" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O49" s="5" t="n">
+      <c r="P49" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P49" s="4" t="n">
+      <c r="Q49" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3340,7 +3494,10 @@
       <c r="L50" s="3" t="n">
         <v>45598</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3348,13 +3505,13 @@
 </t>
         </is>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="O50" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O50" s="2" t="n">
+      <c r="P50" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P50" s="4" t="n">
+      <c r="Q50" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3397,7 +3554,10 @@
       <c r="L51" s="6" t="n">
         <v>45598</v>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3405,13 +3565,13 @@
 </t>
         </is>
       </c>
-      <c r="N51" s="5" t="n">
+      <c r="O51" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O51" s="5" t="n">
+      <c r="P51" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P51" s="4" t="n">
+      <c r="Q51" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3454,7 +3614,10 @@
       <c r="L52" s="3" t="n">
         <v>45601</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3462,13 +3625,13 @@
 </t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="O52" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O52" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P52" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3511,7 +3674,10 @@
       <c r="L53" s="6" t="n">
         <v>45602</v>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3519,13 +3685,13 @@
 </t>
         </is>
       </c>
-      <c r="N53" s="5" t="n">
+      <c r="O53" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O53" s="5" t="n">
+      <c r="P53" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P53" s="4" t="n">
+      <c r="Q53" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3568,7 +3734,10 @@
       <c r="L54" s="3" t="n">
         <v>45603</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3576,13 +3745,13 @@
 </t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="O54" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O54" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P54" s="4" t="n">
+      <c r="Q54" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3625,7 +3794,10 @@
       <c r="L55" s="6" t="n">
         <v>45603</v>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3633,13 +3805,13 @@
 </t>
         </is>
       </c>
-      <c r="N55" s="5" t="n">
+      <c r="O55" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O55" s="5" t="n">
+      <c r="P55" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="Q55" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3682,7 +3854,10 @@
       <c r="L56" s="3" t="n">
         <v>45604</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3690,13 +3865,13 @@
 </t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="O56" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="O56" s="2" t="n">
+      <c r="P56" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P56" s="4" t="n">
+      <c r="Q56" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3739,7 +3914,10 @@
       <c r="L57" s="6" t="n">
         <v>45605</v>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="M57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3747,13 +3925,13 @@
 </t>
         </is>
       </c>
-      <c r="N57" s="5" t="n">
+      <c r="O57" s="5" t="n">
         <v>467</v>
       </c>
-      <c r="O57" s="5" t="n">
+      <c r="P57" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P57" s="4" t="n">
+      <c r="Q57" s="4" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -3796,7 +3974,10 @@
       <c r="L58" s="3" t="n">
         <v>45608</v>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3804,13 +3985,13 @@
 </t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="O58" s="2" t="n">
         <v>316</v>
       </c>
-      <c r="O58" s="2" t="n">
+      <c r="P58" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3853,7 +4034,10 @@
       <c r="L59" s="6" t="n">
         <v>45609</v>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3861,13 +4045,13 @@
 </t>
         </is>
       </c>
-      <c r="N59" s="5" t="n">
+      <c r="O59" s="5" t="n">
         <v>492</v>
       </c>
-      <c r="O59" s="5" t="n">
+      <c r="P59" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P59" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -3910,7 +4094,10 @@
       <c r="L60" s="3" t="n">
         <v>45450</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3918,13 +4105,13 @@
 </t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="O60" s="2" t="n">
         <v>316</v>
       </c>
-      <c r="O60" s="2" t="n">
+      <c r="P60" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="Q60" s="4" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3967,7 +4154,10 @@
       <c r="L61" s="6" t="n">
         <v>45450</v>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -3975,13 +4165,13 @@
 </t>
         </is>
       </c>
-      <c r="N61" s="5" t="n">
+      <c r="O61" s="5" t="n">
         <v>517</v>
       </c>
-      <c r="O61" s="5" t="n">
+      <c r="P61" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P61" s="4" t="n">
+      <c r="Q61" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -4024,7 +4214,10 @@
       <c r="L62" s="3" t="n">
         <v>45450</v>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4032,13 +4225,13 @@
 </t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>660</v>
       </c>
-      <c r="O62" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>560</v>
       </c>
-      <c r="P62" s="4" t="n">
+      <c r="Q62" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4081,7 +4274,10 @@
       <c r="L63" s="6" t="n">
         <v>45433</v>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  TPL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4089,13 +4285,13 @@
 </t>
         </is>
       </c>
-      <c r="N63" s="5" t="n">
+      <c r="O63" s="5" t="n">
         <v>930</v>
       </c>
-      <c r="O63" s="5" t="n">
+      <c r="P63" s="5" t="n">
         <v>780</v>
       </c>
-      <c r="P63" s="4" t="n">
+      <c r="Q63" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -4138,7 +4334,10 @@
       <c r="L64" s="3" t="n">
         <v>45611</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -4146,13 +4345,13 @@
 </t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="O64" s="2" t="n">
         <v>517</v>
       </c>
-      <c r="O64" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P64" s="4" t="n">
+      <c r="Q64" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -4195,7 +4394,10 @@
       <c r="L65" s="6" t="n">
         <v>45611</v>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -4203,13 +4405,13 @@
 </t>
         </is>
       </c>
-      <c r="N65" s="5" t="n">
+      <c r="O65" s="5" t="n">
         <v>517</v>
       </c>
-      <c r="O65" s="5" t="n">
+      <c r="P65" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P65" s="4" t="n">
+      <c r="Q65" s="4" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -4252,7 +4454,10 @@
       <c r="L66" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date       SGL-BUNG       earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers      total price        contract name  
@@ -4261,13 +4466,13 @@
 </t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
-        <v>159.6</v>
-      </c>
       <c r="O66" s="2" t="n">
         <v>159.6</v>
       </c>
       <c r="P66" s="2" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="Q66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4310,7 +4515,10 @@
       <c r="L67" s="6" t="n">
         <v>45647</v>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers   total price    contract name  
@@ -4319,13 +4527,13 @@
 </t>
         </is>
       </c>
-      <c r="N67" s="5" t="n">
-        <v>336</v>
-      </c>
       <c r="O67" s="5" t="n">
         <v>336</v>
       </c>
       <c r="P67" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q67" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4368,7 +4576,10 @@
       <c r="L68" s="3" t="n">
         <v>45489</v>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4376,13 +4587,13 @@
 </t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="O68" s="2" t="n">
         <v>716</v>
       </c>
-      <c r="O68" s="2" t="n">
+      <c r="P68" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="P68" s="4" t="n">
+      <c r="Q68" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4430,15 +4641,18 @@
         <v>45844</v>
       </c>
       <c r="M69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="5" t="n">
         <v/>
       </c>
-      <c r="N69" s="5" t="n">
+      <c r="O69" s="5" t="n">
         <v>1130</v>
       </c>
-      <c r="O69" s="5" t="n">
+      <c r="P69" s="5" t="n">
         <v/>
       </c>
-      <c r="P69" s="4" t="n">
+      <c r="Q69" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -4481,7 +4695,10 @@
       <c r="L70" s="3" t="n">
         <v>45654</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers   total price    contract name  
@@ -4490,13 +4707,13 @@
 </t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
-        <v>336</v>
-      </c>
       <c r="O70" s="2" t="n">
         <v>336</v>
       </c>
       <c r="P70" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4539,7 +4756,10 @@
       <c r="L71" s="6" t="n">
         <v>45655</v>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date       SGL-BUNG       earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -4548,13 +4768,13 @@
 </t>
         </is>
       </c>
-      <c r="N71" s="5" t="n">
-        <v>228</v>
-      </c>
       <c r="O71" s="5" t="n">
         <v>228</v>
       </c>
       <c r="P71" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q71" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4595,7 +4815,10 @@
       <c r="L72" s="3" t="n">
         <v>45481</v>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -4603,13 +4826,13 @@
 </t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
-        <v>392</v>
-      </c>
       <c r="O72" s="2" t="n">
         <v>392</v>
       </c>
       <c r="P72" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q72" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4652,7 +4875,10 @@
       <c r="L73" s="6" t="n">
         <v>45647</v>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="M73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers   total price    contract name  
@@ -4661,13 +4887,13 @@
 </t>
         </is>
       </c>
-      <c r="N73" s="5" t="n">
-        <v>336</v>
-      </c>
       <c r="O73" s="5" t="n">
         <v>336</v>
       </c>
       <c r="P73" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q73" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4710,7 +4936,10 @@
       <c r="L74" s="3" t="n">
         <v>45484</v>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4718,13 +4947,13 @@
 </t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="O74" s="2" t="n">
         <v>716</v>
       </c>
-      <c r="O74" s="2" t="n">
+      <c r="P74" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="P74" s="4" t="n">
+      <c r="Q74" s="4" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4767,7 +4996,10 @@
       <c r="L75" s="6" t="n">
         <v>45479</v>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL(CH)-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4775,13 +5007,13 @@
 </t>
         </is>
       </c>
-      <c r="N75" s="5" t="n">
+      <c r="O75" s="5" t="n">
         <v>1130</v>
       </c>
-      <c r="O75" s="5" t="n">
+      <c r="P75" s="5" t="n">
         <v>980</v>
       </c>
-      <c r="P75" s="4" t="n">
+      <c r="Q75" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -4824,7 +5056,10 @@
       <c r="L76" s="3" t="n">
         <v>45479</v>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL(CH)-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -4832,13 +5067,13 @@
 </t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="O76" s="2" t="n">
         <v>1130</v>
       </c>
-      <c r="O76" s="2" t="n">
+      <c r="P76" s="2" t="n">
         <v>980</v>
       </c>
-      <c r="P76" s="4" t="n">
+      <c r="Q76" s="4" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -4879,7 +5114,10 @@
       <c r="L77" s="6" t="n">
         <v>45611</v>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -4887,13 +5125,13 @@
 </t>
         </is>
       </c>
-      <c r="N77" s="5" t="n">
+      <c r="O77" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="O77" s="5" t="n">
+      <c r="P77" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P77" s="4" t="n">
+      <c r="Q77" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -4934,7 +5172,10 @@
       <c r="L78" s="3" t="n">
         <v>45629</v>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -4942,14 +5183,14 @@
 </t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O78" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P78" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P78" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4989,7 +5230,10 @@
       <c r="L79" s="6" t="n">
         <v>45629</v>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="M79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date       SGL-BUNG       earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -4997,14 +5241,14 @@
 </t>
         </is>
       </c>
-      <c r="N79" s="5" t="n">
-        <v>212.8</v>
-      </c>
       <c r="O79" s="5" t="n">
         <v>212.8</v>
       </c>
-      <c r="P79" s="4" t="n">
-        <v>2.842170943040401e-14</v>
+      <c r="P79" s="5" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5044,7 +5288,10 @@
       <c r="L80" s="3" t="n">
         <v>45629</v>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -5052,14 +5299,14 @@
 </t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O80" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P80" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P80" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5099,7 +5346,10 @@
       <c r="L81" s="6" t="n">
         <v>45656</v>
       </c>
-      <c r="M81" s="5" t="inlineStr">
+      <c r="M81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -5107,14 +5357,14 @@
 </t>
         </is>
       </c>
-      <c r="N81" s="5" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O81" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="P81" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P81" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5154,7 +5404,10 @@
       <c r="L82" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5162,13 +5415,13 @@
 </t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="O82" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="O82" s="2" t="n">
+      <c r="P82" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P82" s="4" t="n">
+      <c r="Q82" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -5209,7 +5462,10 @@
       <c r="L83" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="M83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5217,13 +5473,13 @@
 </t>
         </is>
       </c>
-      <c r="N83" s="5" t="n">
+      <c r="O83" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="O83" s="5" t="n">
+      <c r="P83" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P83" s="4" t="n">
+      <c r="Q83" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -5264,7 +5520,10 @@
       <c r="L84" s="3" t="n">
         <v>45521</v>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5272,13 +5531,13 @@
 </t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="O84" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="O84" s="2" t="n">
+      <c r="P84" s="2" t="n">
         <v>392</v>
       </c>
-      <c r="P84" s="4" t="n">
+      <c r="Q84" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -5319,7 +5578,10 @@
       <c r="L85" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5327,13 +5589,13 @@
 </t>
         </is>
       </c>
-      <c r="N85" s="5" t="n">
+      <c r="O85" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="O85" s="5" t="n">
+      <c r="P85" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P85" s="4" t="n">
+      <c r="Q85" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -5374,7 +5636,10 @@
       <c r="L86" s="3" t="n">
         <v>45589</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5382,13 +5647,13 @@
 </t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="O86" s="2" t="n">
         <v>212.8</v>
       </c>
-      <c r="O86" s="2" t="n">
+      <c r="P86" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="P86" s="4" t="n">
+      <c r="Q86" s="4" t="n">
         <v>53.20000000000002</v>
       </c>
     </row>
@@ -5429,7 +5694,10 @@
       <c r="L87" s="6" t="n">
         <v>45521</v>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -5437,13 +5705,13 @@
 </t>
         </is>
       </c>
-      <c r="N87" s="5" t="n">
+      <c r="O87" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="O87" s="5" t="n">
+      <c r="P87" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P87" s="4" t="n">
+      <c r="Q87" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -5486,7 +5754,10 @@
       <c r="L88" s="3" t="n">
         <v>45631</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -5495,14 +5766,14 @@
 </t>
         </is>
       </c>
-      <c r="N88" s="2" t="n">
-        <v>369.6</v>
-      </c>
       <c r="O88" s="2" t="n">
         <v>369.6</v>
       </c>
-      <c r="P88" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P88" s="2" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5544,7 +5815,10 @@
       <c r="L89" s="6" t="n">
         <v>45657</v>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="M89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers      total price        contract name  
@@ -5553,13 +5827,13 @@
 </t>
         </is>
       </c>
-      <c r="N89" s="5" t="n">
-        <v>470.4</v>
-      </c>
       <c r="O89" s="5" t="n">
         <v>470.4</v>
       </c>
       <c r="P89" s="5" t="n">
+        <v>470.4</v>
+      </c>
+      <c r="Q89" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5602,7 +5876,10 @@
       <c r="L90" s="3" t="n">
         <v>45655</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers      total price        contract name  
@@ -5611,13 +5888,13 @@
 </t>
         </is>
       </c>
-      <c r="N90" s="2" t="n">
-        <v>470.4</v>
-      </c>
       <c r="O90" s="2" t="n">
         <v>470.4</v>
       </c>
       <c r="P90" s="2" t="n">
+        <v>470.4</v>
+      </c>
+      <c r="Q90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5660,7 +5937,10 @@
       <c r="L91" s="6" t="n">
         <v>45639</v>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date       SGL-BUNG       earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights        price         senior  gd  price with offers      total price        contract name  
@@ -5669,13 +5949,13 @@
 </t>
         </is>
       </c>
-      <c r="N91" s="5" t="n">
-        <v>319.2</v>
-      </c>
       <c r="O91" s="5" t="n">
         <v>319.2</v>
       </c>
       <c r="P91" s="5" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="Q91" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5723,15 +6003,18 @@
         <v>45649</v>
       </c>
       <c r="M92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="2" t="n">
         <v/>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="O92" s="2" t="n">
         <v>762.4</v>
       </c>
-      <c r="O92" s="2" t="n">
+      <c r="P92" s="2" t="n">
         <v/>
       </c>
-      <c r="P92" s="4" t="n">
+      <c r="Q92" s="4" t="n">
         <v/>
       </c>
     </row>
@@ -5774,7 +6057,10 @@
       <c r="L93" s="6" t="n">
         <v>45649</v>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -5783,13 +6069,13 @@
 </t>
         </is>
       </c>
-      <c r="N93" s="5" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O93" s="5" t="n">
         <v>548.8</v>
       </c>
       <c r="P93" s="5" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q93" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5832,7 +6118,10 @@
       <c r="L94" s="3" t="n">
         <v>45649</v>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -5841,13 +6130,13 @@
 </t>
         </is>
       </c>
-      <c r="N94" s="2" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O94" s="2" t="n">
         <v>548.8</v>
       </c>
       <c r="P94" s="2" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q94" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5888,7 +6177,10 @@
       <c r="L95" s="6" t="n">
         <v>45557</v>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="M95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -5896,13 +6188,13 @@
 </t>
         </is>
       </c>
-      <c r="N95" s="5" t="n">
+      <c r="O95" s="5" t="n">
         <v>492.8</v>
       </c>
-      <c r="O95" s="5" t="n">
+      <c r="P95" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P95" s="4" t="n">
+      <c r="Q95" s="4" t="n">
         <v>123.2</v>
       </c>
     </row>
@@ -5943,7 +6235,10 @@
       <c r="L96" s="3" t="n">
         <v>45557</v>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="M96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -5951,13 +6246,13 @@
 </t>
         </is>
       </c>
-      <c r="N96" s="2" t="n">
+      <c r="O96" s="2" t="n">
         <v>492.8</v>
       </c>
-      <c r="O96" s="2" t="n">
+      <c r="P96" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="P96" s="4" t="n">
+      <c r="Q96" s="4" t="n">
         <v>123.2</v>
       </c>
     </row>
@@ -5998,7 +6293,10 @@
       <c r="L97" s="6" t="n">
         <v>45557</v>
       </c>
-      <c r="M97" s="5" t="inlineStr">
+      <c r="M97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -6006,13 +6304,13 @@
 </t>
         </is>
       </c>
-      <c r="N97" s="5" t="n">
+      <c r="O97" s="5" t="n">
         <v>334.4</v>
       </c>
-      <c r="O97" s="5" t="n">
+      <c r="P97" s="5" t="n">
         <v>418</v>
       </c>
-      <c r="P97" s="4" t="n">
+      <c r="Q97" s="4" t="n">
         <v>83.60000000000002</v>
       </c>
     </row>
@@ -6053,7 +6351,10 @@
       <c r="L98" s="3" t="n">
         <v>45557</v>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="M98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  SGL-BUNG  earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -6061,13 +6362,13 @@
 </t>
         </is>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="O98" s="2" t="n">
         <v>334.4</v>
       </c>
-      <c r="O98" s="2" t="n">
+      <c r="P98" s="2" t="n">
         <v>418</v>
       </c>
-      <c r="P98" s="4" t="n">
+      <c r="Q98" s="4" t="n">
         <v>83.60000000000002</v>
       </c>
     </row>
@@ -6108,7 +6409,10 @@
       <c r="L99" s="6" t="n">
         <v>45557</v>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -6116,13 +6420,13 @@
 </t>
         </is>
       </c>
-      <c r="N99" s="5" t="n">
+      <c r="O99" s="5" t="n">
         <v>492.8</v>
       </c>
-      <c r="O99" s="5" t="n">
+      <c r="P99" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P99" s="4" t="n">
+      <c r="Q99" s="4" t="n">
         <v>123.2</v>
       </c>
     </row>
@@ -6163,7 +6467,10 @@
       <c r="L100" s="3" t="n">
         <v>45625</v>
       </c>
-      <c r="M100" s="2" t="inlineStr">
+      <c r="M100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price        contract name  
@@ -6171,14 +6478,14 @@
 </t>
         </is>
       </c>
-      <c r="N100" s="2" t="n">
-        <v>492.8</v>
-      </c>
       <c r="O100" s="2" t="n">
         <v>492.8</v>
       </c>
-      <c r="P100" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P100" s="2" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -6218,7 +6525,10 @@
       <c r="L101" s="6" t="n">
         <v>45557</v>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -6226,13 +6536,13 @@
 </t>
         </is>
       </c>
-      <c r="N101" s="5" t="n">
+      <c r="O101" s="5" t="n">
         <v>492.8</v>
       </c>
-      <c r="O101" s="5" t="n">
+      <c r="P101" s="5" t="n">
         <v>616</v>
       </c>
-      <c r="P101" s="4" t="n">
+      <c r="Q101" s="4" t="n">
         <v>123.2</v>
       </c>
     </row>
@@ -6273,7 +6583,10 @@
       <c r="L102" s="3" t="n">
         <v>45557</v>
       </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="M102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price  contract name
@@ -6281,13 +6594,13 @@
 </t>
         </is>
       </c>
-      <c r="N102" s="2" t="n">
+      <c r="O102" s="2" t="n">
         <v>492.8</v>
       </c>
-      <c r="O102" s="2" t="n">
+      <c r="P102" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="P102" s="4" t="n">
+      <c r="Q102" s="4" t="n">
         <v>123.2</v>
       </c>
     </row>
@@ -6330,7 +6643,10 @@
       <c r="L103" s="6" t="n">
         <v>45656</v>
       </c>
-      <c r="M103" s="5" t="inlineStr">
+      <c r="M103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -6339,13 +6655,13 @@
 </t>
         </is>
       </c>
-      <c r="N103" s="5" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O103" s="5" t="n">
         <v>548.8</v>
       </c>
       <c r="P103" s="5" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q103" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6388,7 +6704,10 @@
       <c r="L104" s="3" t="n">
         <v>45653</v>
       </c>
-      <c r="M104" s="2" t="inlineStr">
+      <c r="M104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -6397,13 +6716,13 @@
 </t>
         </is>
       </c>
-      <c r="N104" s="2" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O104" s="2" t="n">
         <v>548.8</v>
       </c>
       <c r="P104" s="2" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q104" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6446,7 +6765,10 @@
       <c r="L105" s="6" t="n">
         <v>45650</v>
       </c>
-      <c r="M105" s="5" t="inlineStr">
+      <c r="M105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -6455,13 +6777,13 @@
 </t>
         </is>
       </c>
-      <c r="N105" s="5" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O105" s="5" t="n">
         <v>548.8</v>
       </c>
       <c r="P105" s="5" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q105" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6504,7 +6826,10 @@
       <c r="L106" s="3" t="n">
         <v>45644</v>
       </c>
-      <c r="M106" s="2" t="inlineStr">
+      <c r="M106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price       contract name  
@@ -6513,13 +6838,13 @@
 </t>
         </is>
       </c>
-      <c r="N106" s="2" t="n">
-        <v>548.8</v>
-      </c>
       <c r="O106" s="2" t="n">
         <v>548.8</v>
       </c>
       <c r="P106" s="2" t="n">
+        <v>548.8</v>
+      </c>
+      <c r="Q106" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6562,7 +6887,10 @@
       <c r="L107" s="6" t="n">
         <v>45660</v>
       </c>
-      <c r="M107" s="5" t="inlineStr">
+      <c r="M107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date  DBL(CH)-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price    contract name  
@@ -6571,13 +6899,13 @@
 </t>
         </is>
       </c>
-      <c r="N107" s="5" t="n">
-        <v>686</v>
-      </c>
       <c r="O107" s="5" t="n">
         <v>686</v>
       </c>
       <c r="P107" s="5" t="n">
+        <v>686</v>
+      </c>
+      <c r="Q107" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6618,7 +6946,10 @@
       <c r="L108" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="M108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6626,14 +6957,14 @@
 </t>
         </is>
       </c>
-      <c r="N108" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O108" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P108" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P108" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6673,7 +7004,10 @@
       <c r="L109" s="6" t="n">
         <v>45659</v>
       </c>
-      <c r="M109" s="5" t="inlineStr">
+      <c r="M109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6681,14 +7015,14 @@
 </t>
         </is>
       </c>
-      <c r="N109" s="5" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O109" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="P109" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P109" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q109" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6728,7 +7062,10 @@
       <c r="L110" s="3" t="n">
         <v>45660</v>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="M110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6736,14 +7073,14 @@
 </t>
         </is>
       </c>
-      <c r="N110" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O110" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P110" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P110" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6783,7 +7120,10 @@
       <c r="L111" s="6" t="n">
         <v>45661</v>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6791,14 +7131,14 @@
 </t>
         </is>
       </c>
-      <c r="N111" s="5" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O111" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="P111" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P111" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6838,7 +7178,10 @@
       <c r="L112" s="3" t="n">
         <v>45664</v>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="M112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6846,14 +7189,14 @@
 </t>
         </is>
       </c>
-      <c r="N112" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O112" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P112" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P112" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6893,7 +7236,10 @@
       <c r="L113" s="6" t="n">
         <v>45664</v>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date       SGL-BUNG       earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6901,14 +7247,14 @@
 </t>
         </is>
       </c>
-      <c r="N113" s="5" t="n">
-        <v>212.8</v>
-      </c>
       <c r="O113" s="5" t="n">
         <v>212.8</v>
       </c>
-      <c r="P113" s="4" t="n">
-        <v>2.842170943040401e-14</v>
+      <c r="P113" s="5" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="Q113" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6948,7 +7294,10 @@
       <c r="L114" s="3" t="n">
         <v>45650</v>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="M114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -6956,14 +7305,14 @@
 </t>
         </is>
       </c>
-      <c r="N114" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O114" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P114" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P114" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -7003,7 +7352,10 @@
       <c r="L115" s="6" t="n">
         <v>45643</v>
       </c>
-      <c r="M115" s="5" t="inlineStr">
+      <c r="M115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -7011,14 +7363,14 @@
 </t>
         </is>
       </c>
-      <c r="N115" s="5" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O115" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="P115" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P115" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q115" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7058,7 +7410,10 @@
       <c r="L116" s="3" t="n">
         <v>45640</v>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="M116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -7066,14 +7421,14 @@
 </t>
         </is>
       </c>
-      <c r="N116" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O116" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P116" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P116" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7113,7 +7468,10 @@
       <c r="L117" s="6" t="n">
         <v>45607</v>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">contract:
 first date  second date  DBL-BUNG   earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price  contract name
@@ -7121,13 +7479,13 @@
 </t>
         </is>
       </c>
-      <c r="N117" s="5" t="n">
+      <c r="O117" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="O117" s="5" t="n">
+      <c r="P117" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="P117" s="4" t="n">
+      <c r="Q117" s="4" t="n">
         <v>78.40000000000003</v>
       </c>
     </row>
@@ -7168,7 +7526,10 @@
       <c r="L118" s="3" t="n">
         <v>45637</v>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -7176,14 +7537,14 @@
 </t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O118" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P118" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P118" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7223,7 +7584,10 @@
       <c r="L119" s="6" t="n">
         <v>45637</v>
       </c>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="M119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -7231,14 +7595,14 @@
 </t>
         </is>
       </c>
-      <c r="N119" s="5" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O119" s="5" t="n">
         <v>313.6</v>
       </c>
-      <c r="P119" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P119" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q119" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7278,7 +7642,10 @@
       <c r="L120" s="3" t="n">
         <v>45632</v>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="M120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights  price  senior  gd  price with offers  total price    contract name  
@@ -7286,14 +7653,14 @@
 </t>
         </is>
       </c>
-      <c r="N120" s="2" t="n">
-        <v>313.6</v>
-      </c>
       <c r="O120" s="2" t="n">
         <v>313.6</v>
       </c>
-      <c r="P120" s="4" t="n">
-        <v>5.684341886080801e-14</v>
+      <c r="P120" s="2" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7335,7 +7702,10 @@
       <c r="L121" s="6" t="n">
         <v>45625</v>
       </c>
-      <c r="M121" s="5" t="inlineStr">
+      <c r="M121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price    contract name  
@@ -7344,14 +7714,14 @@
 </t>
         </is>
       </c>
-      <c r="N121" s="5" t="n">
+      <c r="O121" s="5" t="n">
         <v>683.1999999999999</v>
       </c>
-      <c r="O121" s="5" t="n">
+      <c r="P121" s="5" t="n">
         <v>683.2</v>
       </c>
-      <c r="P121" s="4" t="n">
-        <v>1.13686837721616e-13</v>
+      <c r="Q121" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7393,7 +7763,10 @@
       <c r="L122" s="3" t="n">
         <v>45625</v>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="M122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price    contract name  
@@ -7402,14 +7775,14 @@
 </t>
         </is>
       </c>
-      <c r="N122" s="2" t="n">
+      <c r="O122" s="2" t="n">
         <v>683.1999999999999</v>
       </c>
-      <c r="O122" s="2" t="n">
+      <c r="P122" s="2" t="n">
         <v>683.2</v>
       </c>
-      <c r="P122" s="4" t="n">
-        <v>1.13686837721616e-13</v>
+      <c r="Q122" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7449,7 +7822,10 @@
       <c r="L123" s="6" t="n">
         <v>45659</v>
       </c>
-      <c r="M123" s="5" t="inlineStr">
+      <c r="M123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights   price  senior  gd  price with offers  total price    contract name  
@@ -7457,14 +7833,14 @@
 </t>
         </is>
       </c>
-      <c r="N123" s="5" t="n">
+      <c r="O123" s="5" t="n">
         <v>627.1999999999999</v>
       </c>
-      <c r="O123" s="5" t="n">
+      <c r="P123" s="5" t="n">
         <v>627.2</v>
       </c>
-      <c r="P123" s="4" t="n">
-        <v>1.13686837721616e-13</v>
+      <c r="Q123" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7504,7 +7880,10 @@
       <c r="L124" s="3" t="n">
         <v>45660</v>
       </c>
-      <c r="M124" s="2" t="inlineStr">
+      <c r="M124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">spo24.11 to 31.01:
 first date  second date      DBL-BUNG        earlyBooking1  earlyBooking2  longTerm  reduction1  reduction2  Nights         price         senior  gd  price with offers      total price        contract name  
@@ -7512,13 +7891,13 @@
 </t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
-        <v>448</v>
-      </c>
       <c r="O124" s="2" t="n">
         <v>448</v>
       </c>
       <c r="P124" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q124" s="2" t="n">
         <v>0</v>
       </c>
     </row>
